--- a/tools/importer/reports/import-product-page.report.xlsx
+++ b/tools/importer/reports/import-product-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>product-page</t>
   </si>
   <si>
-    <t>2026-05-20T10:41:24.671Z</t>
+    <t>2026-05-20T11:52:56.709Z</t>
   </si>
   <si>
     <t>Anti-Tracking Software: Block &amp; Remove Cookies | AVG</t>

--- a/tools/importer/reports/import-product-page.report.xlsx
+++ b/tools/importer/reports/import-product-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>product-page</t>
   </si>
   <si>
-    <t>2026-05-20T11:52:56.709Z</t>
+    <t>2026-05-20T12:18:44.133Z</t>
   </si>
   <si>
     <t>Anti-Tracking Software: Block &amp; Remove Cookies | AVG</t>

--- a/tools/importer/reports/import-product-page.report.xlsx
+++ b/tools/importer/reports/import-product-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>product-page</t>
   </si>
   <si>
-    <t>2026-05-20T12:18:44.133Z</t>
+    <t>2026-05-20T13:14:10.659Z</t>
   </si>
   <si>
     <t>Anti-Tracking Software: Block &amp; Remove Cookies | AVG</t>
